--- a/bitemp_register_v06/docs/ontwerpgedachten/CG PF/Replay files/CG_Portfolio_Replay_Data.xlsx
+++ b/bitemp_register_v06/docs/ontwerpgedachten/CG PF/Replay files/CG_Portfolio_Replay_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Bitemporal_2026\bitemp_register_v06\docs\ontwerpgedachten\CG PF\Replay files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A5731D-0291-49D0-801D-F55AF82BD0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C3287C2-3253-43E4-93AF-2731C699DB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gemeente" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,21 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Organisatie!$A$1:$B$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Persoon!$A$1:$C$67</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -13008,6 +13022,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:FD92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13633,7 +13648,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="2" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>37</v>
       </c>
@@ -13867,7 +13882,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="3" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>38</v>
       </c>
@@ -14113,7 +14128,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="4" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>39</v>
       </c>
@@ -14381,7 +14396,7 @@
       <c r="FC4" s="2"/>
       <c r="FD4" s="2"/>
     </row>
-    <row r="5" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>40</v>
       </c>
@@ -14801,7 +14816,7 @@
       <c r="FC5" s="2"/>
       <c r="FD5" s="2"/>
     </row>
-    <row r="6" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>42</v>
       </c>
@@ -15059,7 +15074,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="7" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43</v>
       </c>
@@ -15341,7 +15356,7 @@
       <c r="FC7" s="2"/>
       <c r="FD7" s="2"/>
     </row>
-    <row r="8" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44</v>
       </c>
@@ -15603,7 +15618,7 @@
       <c r="FC8" s="2"/>
       <c r="FD8" s="2"/>
     </row>
-    <row r="9" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45</v>
       </c>
@@ -15869,7 +15884,7 @@
       <c r="FC9" s="2"/>
       <c r="FD9" s="2"/>
     </row>
-    <row r="10" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46</v>
       </c>
@@ -16095,7 +16110,7 @@
       <c r="FC10" s="2"/>
       <c r="FD10" s="2"/>
     </row>
-    <row r="11" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>47</v>
       </c>
@@ -16357,7 +16372,7 @@
       <c r="FC11" s="2"/>
       <c r="FD11" s="2"/>
     </row>
-    <row r="12" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>48</v>
       </c>
@@ -16649,7 +16664,7 @@
       </c>
       <c r="FD12" s="2"/>
     </row>
-    <row r="13" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>49</v>
       </c>
@@ -16873,7 +16888,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="14" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>50</v>
       </c>
@@ -17113,7 +17128,7 @@
       <c r="FC14" s="2"/>
       <c r="FD14" s="2"/>
     </row>
-    <row r="15" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>51</v>
       </c>
@@ -17381,7 +17396,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="16" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>52</v>
       </c>
@@ -17695,7 +17710,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="17" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>53</v>
       </c>
@@ -17951,7 +17966,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="18" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>54</v>
       </c>
@@ -18171,7 +18186,7 @@
       <c r="FC18" s="2"/>
       <c r="FD18" s="2"/>
     </row>
-    <row r="19" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>55</v>
       </c>
@@ -18451,7 +18466,7 @@
       <c r="FC19" s="2"/>
       <c r="FD19" s="2"/>
     </row>
-    <row r="20" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>56</v>
       </c>
@@ -18721,7 +18736,7 @@
       <c r="FC20" s="2"/>
       <c r="FD20" s="2"/>
     </row>
-    <row r="21" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>57</v>
       </c>
@@ -18991,7 +19006,7 @@
       <c r="FC21" s="2"/>
       <c r="FD21" s="2"/>
     </row>
-    <row r="22" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>58</v>
       </c>
@@ -19255,7 +19270,7 @@
       <c r="FC22" s="2"/>
       <c r="FD22" s="2"/>
     </row>
-    <row r="23" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>59</v>
       </c>
@@ -19595,7 +19610,7 @@
       <c r="FC23" s="2"/>
       <c r="FD23" s="2"/>
     </row>
-    <row r="24" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>60</v>
       </c>
@@ -19843,7 +19858,7 @@
       <c r="FC24" s="2"/>
       <c r="FD24" s="2"/>
     </row>
-    <row r="25" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>61</v>
       </c>
@@ -20129,7 +20144,7 @@
       <c r="FC25" s="2"/>
       <c r="FD25" s="2"/>
     </row>
-    <row r="26" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>62</v>
       </c>
@@ -20479,7 +20494,7 @@
       <c r="FC26" s="2"/>
       <c r="FD26" s="2"/>
     </row>
-    <row r="27" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>63</v>
       </c>
@@ -20707,7 +20722,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="28" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>64</v>
       </c>
@@ -20937,7 +20952,7 @@
       <c r="FC28" s="2"/>
       <c r="FD28" s="2"/>
     </row>
-    <row r="29" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>65</v>
       </c>
@@ -21171,7 +21186,7 @@
       <c r="FC29" s="2"/>
       <c r="FD29" s="2"/>
     </row>
-    <row r="30" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>66</v>
       </c>
@@ -21395,7 +21410,7 @@
       <c r="FC30" s="2"/>
       <c r="FD30" s="2"/>
     </row>
-    <row r="31" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>67</v>
       </c>
@@ -21625,7 +21640,7 @@
       <c r="FC31" s="2"/>
       <c r="FD31" s="2"/>
     </row>
-    <row r="32" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>68</v>
       </c>
@@ -22115,7 +22130,7 @@
       <c r="FC33" s="2"/>
       <c r="FD33" s="2"/>
     </row>
-    <row r="34" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>70</v>
       </c>
@@ -22367,7 +22382,7 @@
       <c r="FC34" s="2"/>
       <c r="FD34" s="2"/>
     </row>
-    <row r="35" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>71</v>
       </c>
@@ -22619,7 +22634,7 @@
       <c r="FC35" s="2"/>
       <c r="FD35" s="2"/>
     </row>
-    <row r="36" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>72</v>
       </c>
@@ -22861,7 +22876,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="37" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>73</v>
       </c>
@@ -23077,7 +23092,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="38" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>74</v>
       </c>
@@ -23305,7 +23320,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="39" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>75</v>
       </c>
@@ -23537,7 +23552,7 @@
       <c r="FC39" s="2"/>
       <c r="FD39" s="2"/>
     </row>
-    <row r="40" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>76</v>
       </c>
@@ -23789,7 +23804,7 @@
       <c r="FC40" s="2"/>
       <c r="FD40" s="2"/>
     </row>
-    <row r="41" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>77</v>
       </c>
@@ -24055,7 +24070,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="42" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>78</v>
       </c>
@@ -24289,7 +24304,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="43" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>79</v>
       </c>
@@ -24561,7 +24576,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="44" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>80</v>
       </c>
@@ -24807,7 +24822,7 @@
       <c r="FC44" s="2"/>
       <c r="FD44" s="2"/>
     </row>
-    <row r="45" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>81</v>
       </c>
@@ -25107,7 +25122,7 @@
       <c r="FC45" s="2"/>
       <c r="FD45" s="2"/>
     </row>
-    <row r="46" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>82</v>
       </c>
@@ -25345,7 +25360,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="47" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>83</v>
       </c>
@@ -25575,7 +25590,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="48" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>84</v>
       </c>
@@ -25789,7 +25804,7 @@
       <c r="FC48" s="2"/>
       <c r="FD48" s="2"/>
     </row>
-    <row r="49" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>85</v>
       </c>
@@ -26011,7 +26026,7 @@
       <c r="FC49" s="2"/>
       <c r="FD49" s="2"/>
     </row>
-    <row r="50" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>86</v>
       </c>
@@ -26227,7 +26242,7 @@
       <c r="FC50" s="2"/>
       <c r="FD50" s="2"/>
     </row>
-    <row r="51" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>87</v>
       </c>
@@ -26681,7 +26696,7 @@
       <c r="FC52" s="2"/>
       <c r="FD52" s="2"/>
     </row>
-    <row r="53" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>89</v>
       </c>
@@ -26893,7 +26908,7 @@
       <c r="FC53" s="2"/>
       <c r="FD53" s="2"/>
     </row>
-    <row r="54" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>90</v>
       </c>
@@ -27105,7 +27120,7 @@
       <c r="FC54" s="2"/>
       <c r="FD54" s="2"/>
     </row>
-    <row r="55" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>91</v>
       </c>
@@ -27317,7 +27332,7 @@
       <c r="FC55" s="2"/>
       <c r="FD55" s="2"/>
     </row>
-    <row r="56" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>92</v>
       </c>
@@ -27533,7 +27548,7 @@
       <c r="FC56" s="2"/>
       <c r="FD56" s="2"/>
     </row>
-    <row r="57" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>93</v>
       </c>
@@ -27749,7 +27764,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="58" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>94</v>
       </c>
@@ -27983,7 +27998,7 @@
       <c r="FC58" s="2"/>
       <c r="FD58" s="2"/>
     </row>
-    <row r="59" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>95</v>
       </c>
@@ -28233,7 +28248,7 @@
       <c r="FC59" s="2"/>
       <c r="FD59" s="2"/>
     </row>
-    <row r="60" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>96</v>
       </c>
@@ -28455,7 +28470,7 @@
       <c r="FC60" s="2"/>
       <c r="FD60" s="2"/>
     </row>
-    <row r="61" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>97</v>
       </c>
@@ -28703,7 +28718,7 @@
       <c r="FC61" s="2"/>
       <c r="FD61" s="2"/>
     </row>
-    <row r="62" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>98</v>
       </c>
@@ -28947,7 +28962,7 @@
       <c r="FC62" s="2"/>
       <c r="FD62" s="2"/>
     </row>
-    <row r="63" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>99</v>
       </c>
@@ -29209,7 +29224,7 @@
       <c r="FC63" s="2"/>
       <c r="FD63" s="2"/>
     </row>
-    <row r="64" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>100</v>
       </c>
@@ -29443,7 +29458,7 @@
       <c r="FC64" s="2"/>
       <c r="FD64" s="2"/>
     </row>
-    <row r="65" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>101</v>
       </c>
@@ -29717,7 +29732,7 @@
       <c r="FC65" s="2"/>
       <c r="FD65" s="2"/>
     </row>
-    <row r="66" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>102</v>
       </c>
@@ -29977,7 +29992,7 @@
       <c r="FC66" s="2"/>
       <c r="FD66" s="2"/>
     </row>
-    <row r="67" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>103</v>
       </c>
@@ -30231,7 +30246,7 @@
       <c r="FC67" s="2"/>
       <c r="FD67" s="2"/>
     </row>
-    <row r="68" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>104</v>
       </c>
@@ -30587,7 +30602,7 @@
       <c r="FC68" s="2"/>
       <c r="FD68" s="2"/>
     </row>
-    <row r="69" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>105</v>
       </c>
@@ -30817,7 +30832,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="70" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>106</v>
       </c>
@@ -31083,7 +31098,7 @@
       </c>
       <c r="FD70" s="2"/>
     </row>
-    <row r="71" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>107</v>
       </c>
@@ -31347,7 +31362,7 @@
       <c r="FC71" s="2"/>
       <c r="FD71" s="2"/>
     </row>
-    <row r="72" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>108</v>
       </c>
@@ -31571,7 +31586,7 @@
       <c r="FC72" s="2"/>
       <c r="FD72" s="2"/>
     </row>
-    <row r="73" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>109</v>
       </c>
@@ -31833,7 +31848,7 @@
       <c r="FC73" s="2"/>
       <c r="FD73" s="2"/>
     </row>
-    <row r="74" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>110</v>
       </c>
@@ -32073,7 +32088,7 @@
       <c r="FC74" s="2"/>
       <c r="FD74" s="2"/>
     </row>
-    <row r="75" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>111</v>
       </c>
@@ -32337,7 +32352,7 @@
       <c r="FC75" s="2"/>
       <c r="FD75" s="2"/>
     </row>
-    <row r="76" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>112</v>
       </c>
@@ -32575,7 +32590,7 @@
       <c r="FC76" s="2"/>
       <c r="FD76" s="2"/>
     </row>
-    <row r="77" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>113</v>
       </c>
@@ -32833,7 +32848,7 @@
       <c r="FC77" s="2"/>
       <c r="FD77" s="2"/>
     </row>
-    <row r="78" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>114</v>
       </c>
@@ -33085,7 +33100,7 @@
       <c r="FC78" s="2"/>
       <c r="FD78" s="2"/>
     </row>
-    <row r="79" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>115</v>
       </c>
@@ -33317,7 +33332,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="80" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>116</v>
       </c>
@@ -33571,7 +33586,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="81" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>117</v>
       </c>
@@ -33825,7 +33840,7 @@
       <c r="FC81" s="2"/>
       <c r="FD81" s="2"/>
     </row>
-    <row r="82" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>118</v>
       </c>
@@ -34057,7 +34072,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="83" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>119</v>
       </c>
@@ -34317,7 +34332,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="84" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>120</v>
       </c>
@@ -34543,7 +34558,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="85" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>121</v>
       </c>
@@ -34807,7 +34822,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="86" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>122</v>
       </c>
@@ -35037,7 +35052,7 @@
       <c r="FC86" s="2"/>
       <c r="FD86" s="2"/>
     </row>
-    <row r="87" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>123</v>
       </c>
@@ -35267,7 +35282,7 @@
       <c r="FC87" s="2"/>
       <c r="FD87" s="2"/>
     </row>
-    <row r="88" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>124</v>
       </c>
@@ -35501,7 +35516,7 @@
       <c r="FC88" s="2"/>
       <c r="FD88" s="2"/>
     </row>
-    <row r="89" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>125</v>
       </c>
@@ -35747,7 +35762,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="90" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>126</v>
       </c>
@@ -36025,7 +36040,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="91" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>127</v>
       </c>
@@ -36359,7 +36374,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="92" spans="1:160" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:160" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>128</v>
       </c>
@@ -36610,7 +36625,14 @@
       <c r="FD92" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:FD92" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:FD92" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Datavirtualisatie"/>
+        <filter val="Gemeenschappelijke DataCatalogus (GDC)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
